--- a/data/processed/cleaned_bank_flows.xlsx
+++ b/data/processed/cleaned_bank_flows.xlsx
@@ -546,7 +546,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -591,43 +591,47 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2024-08-13 21:40:00</t>
+          <t>2008-08-13 21:40:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2024-08-13 21:40:00</t>
+          <t>2008-08-13 21:40:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N2" t="n">
-        <v>86000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>86000</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -640,11 +644,15 @@
           <t>周末营业款结算</t>
         </is>
       </c>
-      <c r="U2" t="b">
-        <v>1</v>
-      </c>
-      <c r="V2" t="b">
-        <v>0</v>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -665,7 +673,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -710,43 +718,47 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2024-08-14 22:10:00</t>
+          <t>2008-08-14 22:10:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2024-08-14 22:10:00</t>
+          <t>2008-08-14 22:10:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N3" t="n">
-        <v>124000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>124000</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>舞王歌舞厅</t>
+          <t>舞王俱乐部</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -759,11 +771,15 @@
           <t>包厢酒水收入</t>
         </is>
       </c>
-      <c r="U3" t="b">
-        <v>1</v>
-      </c>
-      <c r="V3" t="b">
-        <v>0</v>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -784,7 +800,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -829,29 +845,33 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2024-08-15 11:20:00</t>
+          <t>2008-08-15 11:20:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2024-08-15 11:20:00</t>
+          <t>2008-08-15 11:20:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N4" t="n">
-        <v>96000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>96000</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -878,11 +898,15 @@
           <t>营业现金缴存</t>
         </is>
       </c>
-      <c r="U4" t="b">
-        <v>1</v>
-      </c>
-      <c r="V4" t="b">
-        <v>0</v>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -903,7 +927,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -938,7 +962,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -948,29 +972,33 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2024-08-16 10:12:00</t>
+          <t>2008-08-16 10:12:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2024-08-16 10:12:00</t>
+          <t>2008-08-16 10:12:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N5" t="n">
-        <v>90000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
@@ -987,16 +1015,21 @@
           <t>罗宇</t>
         </is>
       </c>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
           <t>借款</t>
         </is>
       </c>
-      <c r="U5" t="b">
-        <v>1</v>
-      </c>
-      <c r="V5" t="b">
-        <v>1</v>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -1017,7 +1050,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1052,7 +1085,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1062,29 +1095,33 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2024-08-16 10:18:00</t>
+          <t>2008-08-16 10:18:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2024-08-16 10:18:00</t>
+          <t>2008-08-16 10:18:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N6" t="n">
-        <v>80000</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -1101,16 +1138,21 @@
           <t>陈三一</t>
         </is>
       </c>
+      <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
           <t>货款</t>
         </is>
       </c>
-      <c r="U6" t="b">
-        <v>1</v>
-      </c>
-      <c r="V6" t="b">
-        <v>1</v>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -1131,7 +1173,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1166,7 +1208,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1176,29 +1218,33 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2024-08-16 10:27:00</t>
+          <t>2008-08-16 10:27:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2024-08-16 10:27:00</t>
+          <t>2008-08-16 10:27:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N7" t="n">
-        <v>100000</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -1215,16 +1261,21 @@
           <t>张夏天</t>
         </is>
       </c>
+      <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
           <t>往来款</t>
         </is>
       </c>
-      <c r="U7" t="b">
-        <v>1</v>
-      </c>
-      <c r="V7" t="b">
-        <v>1</v>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1245,7 +1296,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>synthetic/wechat/罗宇/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/罗宇/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1280,7 +1331,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1290,29 +1341,33 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2024-08-17 15:30:00</t>
+          <t>2008-08-17 15:30:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2024-08-17 15:30:00</t>
+          <t>2008-08-17 15:30:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N8" t="n">
-        <v>90000</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>90000</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -1329,16 +1384,21 @@
           <t>何晓初</t>
         </is>
       </c>
+      <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
           <t>还款</t>
         </is>
       </c>
-      <c r="U8" t="b">
-        <v>1</v>
-      </c>
-      <c r="V8" t="b">
-        <v>1</v>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1359,7 +1419,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>synthetic/wechat/陈三一/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/陈三一/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1394,7 +1454,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1404,29 +1464,33 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2024-08-18 09:48:00</t>
+          <t>2008-08-18 09:48:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2024-08-18 09:48:00</t>
+          <t>2008-08-18 09:48:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N9" t="n">
-        <v>80000</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>80000</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -1443,16 +1507,21 @@
           <t>何晓初控制账户</t>
         </is>
       </c>
+      <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
           <t>劳务费</t>
         </is>
       </c>
-      <c r="U9" t="b">
-        <v>1</v>
-      </c>
-      <c r="V9" t="b">
-        <v>1</v>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1473,7 +1542,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张夏天/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张夏天/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1508,7 +1577,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1518,29 +1587,33 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2024-08-18 14:05:00</t>
+          <t>2008-08-18 14:05:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2024-08-18 14:05:00</t>
+          <t>2008-08-18 14:05:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N10" t="n">
-        <v>100000</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1557,16 +1630,21 @@
           <t>何晓初控制账户</t>
         </is>
       </c>
+      <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
           <t>投资款</t>
         </is>
       </c>
-      <c r="U10" t="b">
-        <v>1</v>
-      </c>
-      <c r="V10" t="b">
-        <v>1</v>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1587,7 +1665,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1632,29 +1710,33 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2024-08-19 16:42:00</t>
+          <t>2008-08-19 16:42:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2024-08-19 16:42:00</t>
+          <t>2008-08-19 16:42:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>30000</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1671,16 +1753,21 @@
           <t>ATM</t>
         </is>
       </c>
+      <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
           <t>现金备用</t>
         </is>
       </c>
-      <c r="U11" t="b">
-        <v>1</v>
-      </c>
-      <c r="V11" t="b">
-        <v>1</v>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1701,7 +1788,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>synthetic/wechat/曾黎/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/曾黎/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1746,29 +1833,33 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2024-08-21 10:08:00</t>
+          <t>2008-08-21 10:08:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2024-08-21 10:08:00</t>
+          <t>2008-08-21 10:08:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>30000</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
@@ -1785,16 +1876,21 @@
           <t>现金柜台</t>
         </is>
       </c>
+      <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
           <t>现金存入</t>
         </is>
       </c>
-      <c r="U12" t="b">
-        <v>1</v>
-      </c>
-      <c r="V12" t="b">
-        <v>1</v>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1815,7 +1911,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>synthetic/wechat/李四/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/李四/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1850,7 +1946,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1860,29 +1956,33 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2024-09-06 09:20:00</t>
+          <t>2008-09-06 09:20:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2024-09-06 09:20:00</t>
+          <t>2008-09-06 09:20:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>50000</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1899,16 +1999,21 @@
           <t>江军</t>
         </is>
       </c>
+      <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
           <t>调解赔偿款</t>
         </is>
       </c>
-      <c r="U13" t="b">
-        <v>1</v>
-      </c>
-      <c r="V13" t="b">
-        <v>1</v>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1929,7 +2034,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>synthetic/wechat/老刘/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/老刘/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1964,7 +2069,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1974,29 +2079,33 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2024-09-06 09:31:00</t>
+          <t>2008-09-06 09:31:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2024-09-06 09:31:00</t>
+          <t>2008-09-06 09:31:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>30000</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -2013,16 +2122,21 @@
           <t>汪春蓉</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
           <t>调解赔偿款</t>
         </is>
       </c>
-      <c r="U14" t="b">
-        <v>1</v>
-      </c>
-      <c r="V14" t="b">
-        <v>1</v>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -2043,7 +2157,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>synthetic/wechat/老刘/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/老刘/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2078,7 +2192,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2088,29 +2202,33 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2024-09-06 09:35:00</t>
+          <t>2008-09-06 09:35:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2024-09-06 09:35:00</t>
+          <t>2008-09-06 09:35:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N15" t="n">
-        <v>20000</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>20000</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -2127,16 +2245,21 @@
           <t>赵志高</t>
         </is>
       </c>
+      <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
           <t>调解赔偿款</t>
         </is>
       </c>
-      <c r="U15" t="b">
-        <v>1</v>
-      </c>
-      <c r="V15" t="b">
-        <v>1</v>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -2157,7 +2280,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>synthetic/wechat/老刘/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/老刘/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2192,7 +2315,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2202,29 +2325,33 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2024-09-06 09:39:00</t>
+          <t>2008-09-06 09:39:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2024-09-06 09:39:00</t>
+          <t>2008-09-06 09:39:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N16" t="n">
-        <v>10000</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>10000</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -2241,16 +2368,21 @@
           <t>易承桂</t>
         </is>
       </c>
+      <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
           <t>调解赔偿款</t>
         </is>
       </c>
-      <c r="U16" t="b">
-        <v>1</v>
-      </c>
-      <c r="V16" t="b">
-        <v>1</v>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -2271,7 +2403,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2306,7 +2438,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2316,29 +2448,33 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2024-08-10 18:00:00</t>
+          <t>2008-08-10 18:00:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2024-08-10 18:00:00</t>
+          <t>2008-08-10 18:00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N17" t="n">
-        <v>6800</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>6800</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -2355,16 +2491,21 @@
           <t>罗贤涛</t>
         </is>
       </c>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
           <t>8月工资</t>
         </is>
       </c>
-      <c r="U17" t="b">
-        <v>1</v>
-      </c>
-      <c r="V17" t="b">
-        <v>0</v>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -2385,7 +2526,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2420,7 +2561,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2430,29 +2571,33 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2024-08-10 18:03:00</t>
+          <t>2008-08-10 18:03:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2024-08-10 18:03:00</t>
+          <t>2008-08-10 18:03:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N18" t="n">
-        <v>6200</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>6200</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -2469,16 +2614,21 @@
           <t>李春梅</t>
         </is>
       </c>
+      <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
           <t>8月工资</t>
         </is>
       </c>
-      <c r="U18" t="b">
-        <v>1</v>
-      </c>
-      <c r="V18" t="b">
-        <v>0</v>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
@@ -2499,7 +2649,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2534,7 +2684,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>微信转账</t>
+          <t>银行转账</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2544,29 +2694,33 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2024-08-12 12:00:00</t>
+          <t>2008-08-12 12:00:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2024-08-12 12:00:00</t>
+          <t>2008-08-12 12:00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N19" t="n">
-        <v>42000</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
@@ -2583,16 +2737,21 @@
           <t>深圳市城东物业有限公司</t>
         </is>
       </c>
+      <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
           <t>场地租金</t>
         </is>
       </c>
-      <c r="U19" t="b">
-        <v>1</v>
-      </c>
-      <c r="V19" t="b">
-        <v>0</v>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2613,7 +2772,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>synthetic/wechat/张三/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/张三/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2658,29 +2817,33 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2024-08-20 20:11:00</t>
+          <t>2008-08-20 20:11:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2024-08-20 20:11:00</t>
+          <t>2008-08-20 20:11:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N20" t="n">
-        <v>328</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -2697,16 +2860,21 @@
           <t>粤味轩餐饮</t>
         </is>
       </c>
+      <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr">
         <is>
           <t>商务餐</t>
         </is>
       </c>
-      <c r="U20" t="b">
-        <v>1</v>
-      </c>
-      <c r="V20" t="b">
-        <v>0</v>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -2727,7 +2895,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>synthetic/wechat/李四/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/李四/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2772,29 +2940,33 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2024-08-25 09:00:00</t>
+          <t>2008-08-25 09:00:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2024-08-25 09:00:00</t>
+          <t>2008-08-25 09:00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N21" t="n">
-        <v>12800</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -2811,16 +2983,21 @@
           <t>同乐派出所</t>
         </is>
       </c>
+      <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr">
         <is>
           <t>工资</t>
         </is>
       </c>
-      <c r="U21" t="b">
-        <v>1</v>
-      </c>
-      <c r="V21" t="b">
-        <v>0</v>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -2841,7 +3018,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>synthetic/wechat/李四/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/李四/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2886,29 +3063,33 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2024-08-26 08:30:00</t>
+          <t>2008-08-26 08:30:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2024-08-26 08:30:00</t>
+          <t>2008-08-26 08:30:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N22" t="n">
-        <v>5200</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -2925,16 +3106,21 @@
           <t>中国建设银行深圳分行</t>
         </is>
       </c>
+      <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr">
         <is>
           <t>房贷</t>
         </is>
       </c>
-      <c r="U22" t="b">
-        <v>1</v>
-      </c>
-      <c r="V22" t="b">
-        <v>0</v>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2955,7 +3141,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>synthetic/wechat/李四/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/李四/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3000,29 +3186,33 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2024-08-27 08:30:00</t>
+          <t>2008-08-27 08:30:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2024-08-27 08:30:00</t>
+          <t>2008-08-27 08:30:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N23" t="n">
-        <v>3100</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -3039,16 +3229,21 @@
           <t>平安汽车金融</t>
         </is>
       </c>
+      <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr">
         <is>
           <t>车贷</t>
         </is>
       </c>
-      <c r="U23" t="b">
-        <v>1</v>
-      </c>
-      <c r="V23" t="b">
-        <v>0</v>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -3069,7 +3264,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>synthetic/wechat/李四/TenpayTrades.csv</t>
+          <t>synthetic/bank_flows/李四/TenpayTrades.csv</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3114,29 +3309,33 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2024-08-30 19:25:00</t>
+          <t>2008-08-30 19:25:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2024-08-30 19:25:00</t>
+          <t>2008-08-30 19:25:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>SYN-0</t>
+          <t>ORIG-2008</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>本轮合成数据将案情整体后移，微信交易时间即案情时间。</t>
-        </is>
-      </c>
-      <c r="N24" t="n">
-        <v>456</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
+          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>456</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -3153,16 +3352,21 @@
           <t>百佳超市</t>
         </is>
       </c>
+      <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr">
         <is>
           <t>日用品</t>
         </is>
       </c>
-      <c r="U24" t="b">
-        <v>1</v>
-      </c>
-      <c r="V24" t="b">
-        <v>0</v>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>

--- a/data/processed/cleaned_bank_flows.xlsx
+++ b/data/processed/cleaned_bank_flows.xlsx
@@ -591,22 +591,22 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2008-08-13 21:40:00</t>
+          <t>2024-08-13 21:40:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2008-08-13 21:40:00</t>
+          <t>2024-08-13 21:40:00</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -718,22 +718,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2008-08-14 22:10:00</t>
+          <t>2024-08-14 22:10:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2008-08-14 22:10:00</t>
+          <t>2024-08-14 22:10:00</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -845,22 +845,22 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2008-08-15 11:20:00</t>
+          <t>2024-08-15 11:20:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2008-08-15 11:20:00</t>
+          <t>2024-08-15 11:20:00</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -972,22 +972,22 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2008-08-16 10:12:00</t>
+          <t>2024-08-16 10:12:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2008-08-16 10:12:00</t>
+          <t>2024-08-16 10:12:00</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2008-08-16 10:18:00</t>
+          <t>2024-08-16 10:18:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2008-08-16 10:18:00</t>
+          <t>2024-08-16 10:18:00</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1218,22 +1218,22 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2008-08-16 10:27:00</t>
+          <t>2024-08-16 10:27:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2008-08-16 10:27:00</t>
+          <t>2024-08-16 10:27:00</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1341,22 +1341,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2008-08-17 15:30:00</t>
+          <t>2024-08-17 15:30:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2008-08-17 15:30:00</t>
+          <t>2024-08-17 15:30:00</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1464,22 +1464,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2008-08-18 09:48:00</t>
+          <t>2024-08-18 09:48:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2008-08-18 09:48:00</t>
+          <t>2024-08-18 09:48:00</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1587,22 +1587,22 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2008-08-18 14:05:00</t>
+          <t>2024-08-18 14:05:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2008-08-18 14:05:00</t>
+          <t>2024-08-18 14:05:00</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1710,22 +1710,22 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2008-08-19 16:42:00</t>
+          <t>2024-08-19 16:42:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2008-08-19 16:42:00</t>
+          <t>2024-08-19 16:42:00</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1833,22 +1833,22 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2008-08-21 10:08:00</t>
+          <t>2024-08-21 10:08:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2008-08-21 10:08:00</t>
+          <t>2024-08-21 10:08:00</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1956,22 +1956,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2008-09-06 09:20:00</t>
+          <t>2024-09-06 09:20:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2008-09-06 09:20:00</t>
+          <t>2024-09-06 09:20:00</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2079,22 +2079,22 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2008-09-06 09:31:00</t>
+          <t>2024-09-06 09:31:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2008-09-06 09:31:00</t>
+          <t>2024-09-06 09:31:00</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2202,22 +2202,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2008-09-06 09:35:00</t>
+          <t>2024-09-06 09:35:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2008-09-06 09:35:00</t>
+          <t>2024-09-06 09:35:00</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2325,22 +2325,22 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2008-09-06 09:39:00</t>
+          <t>2024-09-06 09:39:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2008-09-06 09:39:00</t>
+          <t>2024-09-06 09:39:00</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2448,22 +2448,22 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2008-08-10 18:00:00</t>
+          <t>2024-08-10 18:00:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2008-08-10 18:00:00</t>
+          <t>2024-08-10 18:00:00</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2571,22 +2571,22 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2008-08-10 18:03:00</t>
+          <t>2024-08-10 18:03:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2008-08-10 18:03:00</t>
+          <t>2024-08-10 18:03:00</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2694,22 +2694,22 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2008-08-12 12:00:00</t>
+          <t>2024-08-12 12:00:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2008-08-12 12:00:00</t>
+          <t>2024-08-12 12:00:00</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2817,22 +2817,22 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2008-08-20 20:11:00</t>
+          <t>2024-08-20 20:11:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2008-08-20 20:11:00</t>
+          <t>2024-08-20 20:11:00</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2940,22 +2940,22 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2008-08-25 09:00:00</t>
+          <t>2024-08-25 09:00:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2008-08-25 09:00:00</t>
+          <t>2024-08-25 09:00:00</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3063,22 +3063,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2008-08-26 08:30:00</t>
+          <t>2024-08-26 08:30:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2008-08-26 08:30:00</t>
+          <t>2024-08-26 08:30:00</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2008-08-27 08:30:00</t>
+          <t>2024-08-27 08:30:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2008-08-27 08:30:00</t>
+          <t>2024-08-27 08:30:00</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3309,22 +3309,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2008-08-30 19:25:00</t>
+          <t>2024-08-30 19:25:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2008-08-30 19:25:00</t>
+          <t>2024-08-30 19:25:00</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>ORIG-2008</t>
+          <t>FUTURE-16Y</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>合成测试数据已与原始案情时间线对齐：原2023-2024样本整体映射回2007-2008案情节点；交易/通话时间以映射案情时间为准。</t>
+          <t>本轮合成数据将原案整体后移16年，映射案情时间与银行流水/通话记录时间保持一致。</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
